--- a/cortes-madecentro-RH15-Cartagena-medidas-finales.xlsx
+++ b/cortes-madecentro-RH15-Cartagena-medidas-finales.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cortes" sheetId="1" r:id="R60c4fb6338c14e49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rb8448a60c29b4dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control del pedido" sheetId="3" r:id="R88bf30f3948846d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepción y canteo" sheetId="4" r:id="R595868d2e1a4403a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cortes" sheetId="1" r:id="R4580cfa64b06499b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R67bbde3ea0a242f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control del pedido" sheetId="3" r:id="R3eab4aa0f7ae4815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepción y canteo" sheetId="4" r:id="R0d762a819eab4602"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2288,21 +2288,23 @@
     </row>
     <row r="68" ht="66" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>2250</v>
+        <v>830</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>830</v>
+        <v>100</v>
       </c>
       <c r="C68" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="str">
-        <v>Clóset C3-005 · B1 · Fondo RH15 · RH15 · FINAL CON CANTO</v>
+        <v>Clóset C3-025 · B1 · Amarre posterior superior izquierdo · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E68" s="3" t="str">
         <v>Horizontal</v>
       </c>
-      <c r="F68" s="3"/>
+      <c r="F68" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -2432,21 +2434,23 @@
     </row>
     <row r="74" ht="66" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>2250</v>
+        <v>1075</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>1075</v>
+        <v>100</v>
       </c>
       <c r="C74" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="4" t="str">
-        <v>Clóset C3-011 · B2 · Fondo RH15 · RH15 · FINAL CON CANTO</v>
+        <v>Clóset C3-026 · B2 · Amarre posterior superior derecho · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E74" s="3" t="str">
         <v>Horizontal</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
@@ -2812,16 +2816,16 @@
     </row>
     <row r="88" ht="66" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>470</v>
+        <v>2050</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" s="4" t="str">
-        <v>Baño B01 · BAJO · Lateral · RH15 · FINAL CON CANTO</v>
+        <v>Clóset C3-027 · B2 · Montante posterior derecho · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E88" s="3" t="str">
         <v>Horizontal</v>
@@ -2829,29 +2833,23 @@
       <c r="F88" s="3" t="str">
         <v>Flexible 0,45 mm</v>
       </c>
-      <c r="G88" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="H88" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="I88" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
       <c r="J88" s="3"/>
     </row>
     <row r="89" ht="66" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>490</v>
+        <v>2050</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="C89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D89" s="4" t="str">
-        <v>Baño B02 · BAJO · Piso · RH15 · FINAL CON CANTO</v>
+        <v>Clóset C3-028 · B1 · Montante posterior izquierdo · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E89" s="3" t="str">
         <v>Horizontal</v>
@@ -2859,29 +2857,23 @@
       <c r="F89" s="3" t="str">
         <v>Flexible 0,45 mm</v>
       </c>
-      <c r="G89" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="H89" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="I89" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
       <c r="J89" s="3"/>
     </row>
     <row r="90" ht="66" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>490</v>
+        <v>830</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>405</v>
+        <v>100</v>
       </c>
       <c r="C90" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D90" s="4" t="str">
-        <v>Baño B03 · BAJO · Entrepaño retranqueado con reserva de sifón · RH15 · FINAL CON CANTO</v>
+        <v>Clóset C3-029 · B1 · Amarre posterior inferior izquierdo · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E90" s="3" t="str">
         <v>Horizontal</v>
@@ -2889,29 +2881,23 @@
       <c r="F90" s="3" t="str">
         <v>Flexible 0,45 mm</v>
       </c>
-      <c r="G90" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="H90" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="I90" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
       <c r="J90" s="3"/>
     </row>
     <row r="91" ht="66" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>195</v>
+        <v>1075</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="str">
-        <v>Baño B04 · BAJO · Travesaño trasero superior lateral · RH15 · FINAL CON CANTO</v>
+        <v>Clóset C3-030 · B2 · Amarre posterior inferior derecho · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E91" s="3" t="str">
         <v>Horizontal</v>
@@ -2919,29 +2905,23 @@
       <c r="F91" s="3" t="str">
         <v>Flexible 0,45 mm</v>
       </c>
-      <c r="G91" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="H91" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
-      <c r="I91" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
-      </c>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
       <c r="J91" s="3"/>
     </row>
     <row r="92" ht="66" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" s="4" t="str">
-        <v>Baño B05 · BAJO · Travesaño trasero inferior · RH15 · FINAL CON CANTO</v>
+        <v>Baño B01 · BAJO · Lateral · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E92" s="3" t="str">
         <v>Horizontal</v>
@@ -2962,46 +2942,46 @@
     </row>
     <row r="93" ht="66" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>299</v>
+        <v>490</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>517</v>
+        <v>450</v>
       </c>
       <c r="C93" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D93" s="4" t="str">
-        <v>Baño B06 · BAJO · Panel común para dos puertas: corte diagonal en armado · RH15 · FINAL CON CANTO</v>
+        <v>Baño B02 · BAJO · Piso · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E93" s="3" t="str">
         <v>Horizontal</v>
       </c>
       <c r="F93" s="3" t="str">
-        <v>Rígido 2 mm</v>
+        <v>Flexible 0,45 mm</v>
       </c>
       <c r="G93" s="3" t="str">
-        <v>Rígido 2 mm</v>
+        <v>Flexible 0,45 mm</v>
       </c>
       <c r="H93" s="3" t="str">
-        <v>Rígido 2 mm</v>
+        <v>Flexible 0,45 mm</v>
       </c>
       <c r="I93" s="3" t="str">
-        <v>Rígido 2 mm</v>
+        <v>Flexible 0,45 mm</v>
       </c>
       <c r="J93" s="3"/>
     </row>
     <row r="94" ht="66" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>105</v>
+        <v>405</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="4" t="str">
-        <v>Baño S01 · ESPEJO · Lateral gabinete superior · RH15 · FINAL CON CANTO</v>
+        <v>Baño B03 · BAJO · Entrepaño retranqueado con reserva de sifón · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E94" s="3" t="str">
         <v>Horizontal</v>
@@ -3022,16 +3002,16 @@
     </row>
     <row r="95" ht="66" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>420</v>
+        <v>195</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C95" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D95" s="4" t="str">
-        <v>Baño S02 · ESPEJO · Piso y techo gabinete superior · RH15 · FINAL CON CANTO</v>
+        <v>Baño B04 · BAJO · Travesaño trasero superior lateral · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E95" s="3" t="str">
         <v>Horizontal</v>
@@ -3052,16 +3032,16 @@
     </row>
     <row r="96" ht="66" customHeight="1">
       <c r="A96" s="5" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C96" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D96" s="4" t="str">
-        <v>Baño S03 · ESPEJO · División vertical · RH15 · FINAL CON CANTO</v>
+        <v>Baño B05 · BAJO · Travesaño trasero inferior · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E96" s="3" t="str">
         <v>Horizontal</v>
@@ -3082,46 +3062,46 @@
     </row>
     <row r="97" ht="66" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>100</v>
+        <v>517</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" s="4" t="str">
-        <v>Baño S04 · ESPEJO · Entrepaño interior izquierdo · RH15 · FINAL CON CANTO</v>
+        <v>Baño B06 · BAJO · Panel común para dos puertas: corte diagonal en armado · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E97" s="3" t="str">
         <v>Horizontal</v>
       </c>
       <c r="F97" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
+        <v>Rígido 2 mm</v>
       </c>
       <c r="G97" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
+        <v>Rígido 2 mm</v>
       </c>
       <c r="H97" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
+        <v>Rígido 2 mm</v>
       </c>
       <c r="I97" s="3" t="str">
-        <v>Flexible 0,45 mm</v>
+        <v>Rígido 2 mm</v>
       </c>
       <c r="J97" s="3"/>
     </row>
     <row r="98" ht="66" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" s="4" t="str">
-        <v>Baño S05 · ESPEJO · Entrepaño columna abierta derecha · RH15 · FINAL CON CANTO</v>
+        <v>Baño S01 · ESPEJO · Lateral gabinete superior · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E98" s="3" t="str">
         <v>Horizontal</v>
@@ -3142,16 +3122,16 @@
     </row>
     <row r="99" ht="66" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>320</v>
+        <v>105</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" s="4" t="str">
-        <v>Baño S06 · ESPEJO · Tapa RH15 portadora del espejo · RH15 · FINAL CON CANTO</v>
+        <v>Baño S02 · ESPEJO · Piso y techo gabinete superior · RH15 · FINAL CON CANTO</v>
       </c>
       <c r="E99" s="3" t="str">
         <v>Horizontal</v>
@@ -3170,8 +3150,128 @@
       </c>
       <c r="J99" s="3"/>
     </row>
+    <row r="100" ht="66" customHeight="1">
+      <c r="A100" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="4" t="str">
+        <v>Baño S03 · ESPEJO · División vertical · RH15 · FINAL CON CANTO</v>
+      </c>
+      <c r="E100" s="3" t="str">
+        <v>Horizontal</v>
+      </c>
+      <c r="F100" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="G100" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="H100" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="I100" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="J100" s="3"/>
+    </row>
+    <row r="101" ht="66" customHeight="1">
+      <c r="A101" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" s="4" t="str">
+        <v>Baño S04 · ESPEJO · Entrepaño interior izquierdo · RH15 · FINAL CON CANTO</v>
+      </c>
+      <c r="E101" s="3" t="str">
+        <v>Horizontal</v>
+      </c>
+      <c r="F101" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="G101" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="H101" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="I101" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="J101" s="3"/>
+    </row>
+    <row r="102" ht="66" customHeight="1">
+      <c r="A102" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="4" t="str">
+        <v>Baño S05 · ESPEJO · Entrepaño columna abierta derecha · RH15 · FINAL CON CANTO</v>
+      </c>
+      <c r="E102" s="3" t="str">
+        <v>Horizontal</v>
+      </c>
+      <c r="F102" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="G102" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="H102" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="I102" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="J102" s="3"/>
+    </row>
+    <row r="103" ht="66" customHeight="1">
+      <c r="A103" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" s="4" t="str">
+        <v>Baño S06 · ESPEJO · Tapa RH15 portadora del espejo · RH15 · FINAL CON CANTO</v>
+      </c>
+      <c r="E103" s="3" t="str">
+        <v>Horizontal</v>
+      </c>
+      <c r="F103" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="G103" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="H103" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="I103" s="3" t="str">
+        <v>Flexible 0,45 mm</v>
+      </c>
+      <c r="J103" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J103"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3903,7 +4003,7 @@
         <x:v>Origen</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Pedido único del proyecto. Revisión local del 27/10/2026: un solo tipo de canto por pieza, contrastado con los tres despieces y manifiestos 3D.</x:v>
+        <x:v>Pedido único del proyecto, revisión del 28/10/2026: clóset sin panel trasero, con marco completo C3-025 a C3-030. Sustituye las piezas C3-005 y C3-011 del PDF anterior. Un solo tipo de canto por pieza; contrastado con los tres despieces y manifiestos 3D.</x:v>
       </x:c>
       <x:c r="C5" s="8"/>
       <x:c r="D5" s="8"/>
@@ -3925,8 +4025,8 @@
         <x:v>Cantidad total</x:v>
       </x:c>
       <x:c r="B7" s="10" t="n">
-        <x:f>SUM(Cortes!C2:C99)</x:f>
-        <x:v>141</x:v>
+        <x:f>SUM(Cortes!C2:C103)</x:f>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C7" s="8"/>
       <x:c r="D7" s="8"/>
@@ -3937,8 +4037,8 @@
         <x:v>Referencias</x:v>
       </x:c>
       <x:c r="B8" s="10" t="n">
-        <x:f>COUNT(Cortes!A2:A99)</x:f>
-        <x:v>98</x:v>
+        <x:f>COUNT(Cortes!A2:A103)</x:f>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C8" s="8"/>
       <x:c r="D8" s="8"/>
@@ -4082,7 +4182,7 @@
         <x:v>150 × 99,1</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 150 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 150 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="38" customHeight="1">
@@ -4150,7 +4250,7 @@
         <x:v>570 × 99,55</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 570 × 99.55 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 570 × 99,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="90" customHeight="1">
@@ -4184,7 +4284,7 @@
         <x:v>570 × 79,55</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 570 × 79.55 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 570 × 79,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="90" customHeight="1">
@@ -4252,7 +4352,7 @@
         <x:v>640 × 99,1</x:v>
       </x:c>
       <x:c r="E29" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 640 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 640 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="38" customHeight="1">
@@ -4303,7 +4403,7 @@
         <x:v>549,55 × 74,55</x:v>
       </x:c>
       <x:c r="E32" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 549.55 × 74.55 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 549,55 × 74,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="90" customHeight="1">
@@ -4320,7 +4420,7 @@
         <x:v>583 × 74,55</x:v>
       </x:c>
       <x:c r="E33" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 583 × 74.55 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 583 × 74,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="38" customHeight="1">
@@ -4422,7 +4522,7 @@
         <x:v>669,1 × 99,1</x:v>
       </x:c>
       <x:c r="E39" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 669.1 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 669,1 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="38" customHeight="1">
@@ -4524,7 +4624,7 @@
         <x:v>370 × 99,1</x:v>
       </x:c>
       <x:c r="E45" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 370 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Si no la cantean: cortar a 370 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="90" customHeight="1">
@@ -4609,7 +4709,7 @@
         <x:v>1274,1 × 96,1</x:v>
       </x:c>
       <x:c r="E50" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 1274.1 × 96.1 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 1274,1 × 96,1 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="38" customHeight="1">
@@ -4779,7 +4879,7 @@
         <x:v>569,1 × 59,1</x:v>
       </x:c>
       <x:c r="E60" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 569.1 × 59.1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</x:v>
+        <x:v>Si no la cantean: cortar a 569,1 × 59,1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="38" customHeight="1">
@@ -4875,7 +4975,7 @@
         <x:v>S3 Alacena 65,5 · Puerta izquierda</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>717 × 324.5</x:v>
+        <x:v>717 × 324,5</x:v>
       </x:c>
       <x:c r="D66" s="10" t="str">
         <x:v>713 × 320,5</x:v>
@@ -4892,7 +4992,7 @@
         <x:v>S3 Alacena 65,5 · Puerta derecha</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>717 × 324.5</x:v>
+        <x:v>717 × 324,5</x:v>
       </x:c>
       <x:c r="D67" s="10" t="str">
         <x:v>713 × 320,5</x:v>
@@ -4949,7 +5049,7 @@
         <x:v>684,1 × 59,1</x:v>
       </x:c>
       <x:c r="E70" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 684.1 × 59.1 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 684,1 × 59,1 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="90" customHeight="1">
@@ -4966,7 +5066,7 @@
         <x:v>684,1 × 79,1</x:v>
       </x:c>
       <x:c r="E71" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 684.1 × 79.1 y cantear en el armado.</x:v>
+        <x:v>Si no la cantean: cortar a 684,1 × 79,1 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="38" customHeight="1">
@@ -4977,7 +5077,7 @@
         <x:v>S4 Platero 71,5 · Puerta izquierda</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>717 × 354.5</x:v>
+        <x:v>717 × 354,5</x:v>
       </x:c>
       <x:c r="D72" s="10" t="str">
         <x:v>713 × 350,5</x:v>
@@ -4994,7 +5094,7 @@
         <x:v>S4 Platero 71,5 · Puerta derecha</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>717 × 354.5</x:v>
+        <x:v>717 × 354,5</x:v>
       </x:c>
       <x:c r="D73" s="10" t="str">
         <x:v>713 × 350,5</x:v>
@@ -5156,21 +5256,21 @@
         <x:v>—</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="38" customHeight="1">
+    <x:row r="83" ht="90" customHeight="1">
       <x:c r="A83" s="8" t="str">
-        <x:v>Clóset C3-005</x:v>
+        <x:v>Clóset C3-025</x:v>
       </x:c>
       <x:c r="B83" s="10" t="str">
-        <x:v>B1 · Fondo RH15</x:v>
+        <x:v>B1 · Amarre posterior superior izquierdo</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>2250 × 830</x:v>
+        <x:v>830 × 100</x:v>
       </x:c>
       <x:c r="D83" s="10" t="str">
-        <x:v>2250 × 830</x:v>
+        <x:v>830 × 99,55</x:v>
       </x:c>
       <x:c r="E83" s="10" t="str">
-        <x:v>—</x:v>
+        <x:v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="38" customHeight="1">
@@ -5258,21 +5358,21 @@
         <x:v>—</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="38" customHeight="1">
+    <x:row r="89" ht="90" customHeight="1">
       <x:c r="A89" s="8" t="str">
-        <x:v>Clóset C3-011</x:v>
+        <x:v>Clóset C3-026</x:v>
       </x:c>
       <x:c r="B89" s="10" t="str">
-        <x:v>B2 · Fondo RH15</x:v>
+        <x:v>B2 · Amarre posterior superior derecho</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>2250 × 1075</x:v>
+        <x:v>1075 × 100</x:v>
       </x:c>
       <x:c r="D89" s="10" t="str">
-        <x:v>2250 × 1075</x:v>
+        <x:v>1075 × 99,55</x:v>
       </x:c>
       <x:c r="E89" s="10" t="str">
-        <x:v>—</x:v>
+        <x:v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="38" customHeight="1">
@@ -5498,235 +5598,303 @@
     </x:row>
     <x:row r="103" ht="90" customHeight="1">
       <x:c r="A103" s="8" t="str">
-        <x:v>Baño B01</x:v>
+        <x:v>Clóset C3-027</x:v>
       </x:c>
       <x:c r="B103" s="10" t="str">
-        <x:v>BAJO · Lateral</x:v>
+        <x:v>B2 · Montante posterior derecho</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>470 × 450</x:v>
+        <x:v>2050 × 100</x:v>
       </x:c>
       <x:c r="D103" s="10" t="str">
-        <x:v>469,1 × 449,1</x:v>
+        <x:v>2050 × 99,55</x:v>
       </x:c>
       <x:c r="E103" s="10" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="90" customHeight="1">
       <x:c r="A104" s="8" t="str">
-        <x:v>Baño B02</x:v>
+        <x:v>Clóset C3-028</x:v>
       </x:c>
       <x:c r="B104" s="10" t="str">
-        <x:v>BAJO · Piso</x:v>
+        <x:v>B1 · Montante posterior izquierdo</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>490 × 450</x:v>
+        <x:v>2050 × 100</x:v>
       </x:c>
       <x:c r="D104" s="10" t="str">
-        <x:v>489,1 × 449,1</x:v>
+        <x:v>2050 × 99,55</x:v>
       </x:c>
       <x:c r="E104" s="10" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="90" customHeight="1">
       <x:c r="A105" s="8" t="str">
-        <x:v>Baño B03</x:v>
+        <x:v>Clóset C3-029</x:v>
       </x:c>
       <x:c r="B105" s="10" t="str">
-        <x:v>BAJO · Entrepaño retranqueado con reserva de sifón</x:v>
+        <x:v>B1 · Amarre posterior inferior izquierdo</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>490 × 405</x:v>
+        <x:v>830 × 100</x:v>
       </x:c>
       <x:c r="D105" s="10" t="str">
-        <x:v>489,1 × 404,1</x:v>
+        <x:v>830 × 99,55</x:v>
       </x:c>
       <x:c r="E105" s="10" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="90" customHeight="1">
       <x:c r="A106" s="8" t="str">
-        <x:v>Baño B04</x:v>
+        <x:v>Clóset C3-030</x:v>
       </x:c>
       <x:c r="B106" s="10" t="str">
-        <x:v>BAJO · Travesaño trasero superior lateral</x:v>
+        <x:v>B2 · Amarre posterior inferior derecho</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>195 × 80</x:v>
+        <x:v>1075 × 100</x:v>
       </x:c>
       <x:c r="D106" s="10" t="str">
-        <x:v>194,1 × 79,1</x:v>
+        <x:v>1075 × 99,55</x:v>
       </x:c>
       <x:c r="E106" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="90" customHeight="1">
       <x:c r="A107" s="8" t="str">
-        <x:v>Baño B05</x:v>
+        <x:v>Baño B01</x:v>
       </x:c>
       <x:c r="B107" s="10" t="str">
-        <x:v>BAJO · Travesaño trasero inferior</x:v>
+        <x:v>BAJO · Lateral</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>490 × 80</x:v>
+        <x:v>470 × 450</x:v>
       </x:c>
       <x:c r="D107" s="10" t="str">
-        <x:v>489,1 × 79,1</x:v>
+        <x:v>469,1 × 449,1</x:v>
       </x:c>
       <x:c r="E107" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="90" customHeight="1">
       <x:c r="A108" s="8" t="str">
-        <x:v>Baño B06</x:v>
+        <x:v>Baño B02</x:v>
       </x:c>
       <x:c r="B108" s="10" t="str">
-        <x:v>BAJO · Panel común para dos puertas: corte diagonal en armado</x:v>
+        <x:v>BAJO · Piso</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>299 × 517</x:v>
+        <x:v>490 × 450</x:v>
       </x:c>
       <x:c r="D108" s="10" t="str">
-        <x:v>295 × 513</x:v>
+        <x:v>489,1 × 449,1</x:v>
       </x:c>
       <x:c r="E108" s="10" t="str">
-        <x:v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</x:v>
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="90" customHeight="1">
       <x:c r="A109" s="8" t="str">
-        <x:v>Baño S01</x:v>
+        <x:v>Baño B03</x:v>
       </x:c>
       <x:c r="B109" s="10" t="str">
-        <x:v>ESPEJO · Lateral gabinete superior</x:v>
+        <x:v>BAJO · Entrepaño retranqueado con reserva de sifón</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>500 × 105</x:v>
+        <x:v>490 × 405</x:v>
       </x:c>
       <x:c r="D109" s="10" t="str">
-        <x:v>499,1 × 104,1</x:v>
+        <x:v>489,1 × 404,1</x:v>
       </x:c>
       <x:c r="E109" s="10" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="90" customHeight="1">
       <x:c r="A110" s="8" t="str">
-        <x:v>Baño S02</x:v>
+        <x:v>Baño B04</x:v>
       </x:c>
       <x:c r="B110" s="10" t="str">
-        <x:v>ESPEJO · Piso y techo gabinete superior</x:v>
+        <x:v>BAJO · Travesaño trasero superior lateral</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>420 × 105</x:v>
+        <x:v>195 × 80</x:v>
       </x:c>
       <x:c r="D110" s="10" t="str">
-        <x:v>419,1 × 104,1</x:v>
+        <x:v>194,1 × 79,1</x:v>
       </x:c>
       <x:c r="E110" s="10" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="90" customHeight="1">
       <x:c r="A111" s="8" t="str">
-        <x:v>Baño S03</x:v>
+        <x:v>Baño B05</x:v>
       </x:c>
       <x:c r="B111" s="10" t="str">
-        <x:v>ESPEJO · División vertical</x:v>
+        <x:v>BAJO · Travesaño trasero inferior</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>470 × 105</x:v>
+        <x:v>490 × 80</x:v>
       </x:c>
       <x:c r="D111" s="10" t="str">
-        <x:v>469,1 × 104,1</x:v>
+        <x:v>489,1 × 79,1</x:v>
       </x:c>
       <x:c r="E111" s="10" t="str">
-        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="90" customHeight="1">
       <x:c r="A112" s="8" t="str">
-        <x:v>Baño S04</x:v>
+        <x:v>Baño B06</x:v>
       </x:c>
       <x:c r="B112" s="10" t="str">
-        <x:v>ESPEJO · Entrepaño interior izquierdo</x:v>
+        <x:v>BAJO · Panel común para dos puertas: corte diagonal en armado</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>290 × 100</x:v>
+        <x:v>299 × 517</x:v>
       </x:c>
       <x:c r="D112" s="10" t="str">
-        <x:v>289,1 × 99,1</x:v>
+        <x:v>295 × 513</x:v>
       </x:c>
       <x:c r="E112" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="90" customHeight="1">
       <x:c r="A113" s="8" t="str">
-        <x:v>Baño S05</x:v>
+        <x:v>Baño S01</x:v>
       </x:c>
       <x:c r="B113" s="10" t="str">
-        <x:v>ESPEJO · Entrepaño columna abierta derecha</x:v>
+        <x:v>ESPEJO · Lateral gabinete superior</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>115 × 100</x:v>
+        <x:v>500 × 105</x:v>
       </x:c>
       <x:c r="D113" s="10" t="str">
-        <x:v>114,1 × 99,1</x:v>
+        <x:v>499,1 × 104,1</x:v>
       </x:c>
       <x:c r="E113" s="10" t="str">
-        <x:v>Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="90" customHeight="1">
       <x:c r="A114" s="8" t="str">
+        <x:v>Baño S02</x:v>
+      </x:c>
+      <x:c r="B114" s="10" t="str">
+        <x:v>ESPEJO · Piso y techo gabinete superior</x:v>
+      </x:c>
+      <x:c r="C114" s="10" t="str">
+        <x:v>420 × 105</x:v>
+      </x:c>
+      <x:c r="D114" s="10" t="str">
+        <x:v>419,1 × 104,1</x:v>
+      </x:c>
+      <x:c r="E114" s="10" t="str">
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="90" customHeight="1">
+      <x:c r="A115" s="8" t="str">
+        <x:v>Baño S03</x:v>
+      </x:c>
+      <x:c r="B115" s="10" t="str">
+        <x:v>ESPEJO · División vertical</x:v>
+      </x:c>
+      <x:c r="C115" s="10" t="str">
+        <x:v>470 × 105</x:v>
+      </x:c>
+      <x:c r="D115" s="10" t="str">
+        <x:v>469,1 × 104,1</x:v>
+      </x:c>
+      <x:c r="E115" s="10" t="str">
+        <x:v>Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="90" customHeight="1">
+      <x:c r="A116" s="8" t="str">
+        <x:v>Baño S04</x:v>
+      </x:c>
+      <x:c r="B116" s="10" t="str">
+        <x:v>ESPEJO · Entrepaño interior izquierdo</x:v>
+      </x:c>
+      <x:c r="C116" s="10" t="str">
+        <x:v>290 × 100</x:v>
+      </x:c>
+      <x:c r="D116" s="10" t="str">
+        <x:v>289,1 × 99,1</x:v>
+      </x:c>
+      <x:c r="E116" s="10" t="str">
+        <x:v>Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="90" customHeight="1">
+      <x:c r="A117" s="8" t="str">
+        <x:v>Baño S05</x:v>
+      </x:c>
+      <x:c r="B117" s="10" t="str">
+        <x:v>ESPEJO · Entrepaño columna abierta derecha</x:v>
+      </x:c>
+      <x:c r="C117" s="10" t="str">
+        <x:v>115 × 100</x:v>
+      </x:c>
+      <x:c r="D117" s="10" t="str">
+        <x:v>114,1 × 99,1</x:v>
+      </x:c>
+      <x:c r="E117" s="10" t="str">
+        <x:v>Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="90" customHeight="1">
+      <x:c r="A118" s="8" t="str">
         <x:v>Baño S06</x:v>
       </x:c>
-      <x:c r="B114" s="10" t="str">
+      <x:c r="B118" s="10" t="str">
         <x:v>ESPEJO · Tapa RH15 portadora del espejo</x:v>
       </x:c>
-      <x:c r="C114" s="10" t="str">
+      <x:c r="C118" s="10" t="str">
         <x:v>500 × 320</x:v>
       </x:c>
-      <x:c r="D114" s="10" t="str">
+      <x:c r="D118" s="10" t="str">
         <x:v>499,1 × 319,1</x:v>
       </x:c>
-      <x:c r="E114" s="10" t="str">
+      <x:c r="E118" s="10" t="str">
         <x:v>Medida exterior de referencia 320 × 500; espejo pegado en cara exterior. Dos bisagras candidatas, peso conjunto aproximado 2,8 kg sin herrajes. Validar holguras, cazoletas y adhesivo compatible con espejo. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="8"/>
-      <x:c r="B115" s="8"/>
-      <x:c r="C115" s="8"/>
-      <x:c r="D115" s="8"/>
-      <x:c r="E115" s="8"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="8"/>
-      <x:c r="B116" s="8"/>
-      <x:c r="C116" s="8"/>
-      <x:c r="D116" s="8"/>
-      <x:c r="E116" s="8"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="8"/>
-      <x:c r="B117" s="8"/>
-      <x:c r="C117" s="8"/>
-      <x:c r="D117" s="8"/>
-      <x:c r="E117" s="8"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="8"/>
-      <x:c r="B118" s="8"/>
-      <x:c r="C118" s="8"/>
-      <x:c r="D118" s="8"/>
-      <x:c r="E118" s="8"/>
+    <x:row r="119">
+      <x:c r="A119" s="8"/>
+      <x:c r="B119" s="8"/>
+      <x:c r="C119" s="8"/>
+      <x:c r="D119" s="8"/>
+      <x:c r="E119" s="8"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="8"/>
+      <x:c r="B120" s="8"/>
+      <x:c r="C120" s="8"/>
+      <x:c r="D120" s="8"/>
+      <x:c r="E120" s="8"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="8"/>
+      <x:c r="B121" s="8"/>
+      <x:c r="C121" s="8"/>
+      <x:c r="D121" s="8"/>
+      <x:c r="E121" s="8"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="8"/>
+      <x:c r="B122" s="8"/>
+      <x:c r="C122" s="8"/>
+      <x:c r="D122" s="8"/>
+      <x:c r="E122" s="8"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5836,15 +6004,15 @@
       </x:c>
       <x:c r="B4" s="8"/>
       <x:c r="C4" s="8" t="n">
-        <x:f>COUNTIFS(P10:P107,"POR REVISAR")</x:f>
-        <x:v>96</x:v>
+        <x:f>COUNTIFS(P10:P111,"POR REVISAR")</x:f>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
         <x:v>Rígido neto m</x:v>
       </x:c>
       <x:c r="E4" s="8"/>
       <x:c r="F4" s="8" t="str">
-        <x:f>IF(C4&gt;0,"Revisar entrega",SUM(N10:N107))</x:f>
+        <x:f>IF(C4&gt;0,"Revisar entrega",SUM(N10:N111))</x:f>
         <x:v>Revisar entrega</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
@@ -5852,7 +6020,7 @@
       </x:c>
       <x:c r="H4" s="8"/>
       <x:c r="I4" s="8" t="str">
-        <x:f>IF(C4&gt;0,"Revisar entrega",SUMPRODUCT(J10:J107,--(F10:F107="R"))+SUMPRODUCT(K10:K107,--(G10:G107="R"))+SUMPRODUCT(L10:L107,--(H10:H107="R"))+SUMPRODUCT(M10:M107,--(I10:I107="R")))</x:f>
+        <x:f>IF(C4&gt;0,"Revisar entrega",SUMPRODUCT(J10:J111,--(F10:F111="R"))+SUMPRODUCT(K10:K111,--(G10:G111="R"))+SUMPRODUCT(L10:L111,--(H10:H111="R"))+SUMPRODUCT(M10:M111,--(I10:I111="R")))</x:f>
         <x:v>Revisar entrega</x:v>
       </x:c>
       <x:c r="J4" s="8" t="str">
@@ -5887,7 +6055,7 @@
       </x:c>
       <x:c r="E5" s="8"/>
       <x:c r="F5" s="8" t="str">
-        <x:f>IF(C4&gt;0,"Revisar entrega",SUM(O10:O107))</x:f>
+        <x:f>IF(C4&gt;0,"Revisar entrega",SUM(O10:O111))</x:f>
         <x:v>Revisar entrega</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
@@ -5895,7 +6063,7 @@
       </x:c>
       <x:c r="H5" s="8"/>
       <x:c r="I5" s="8" t="str">
-        <x:f>IF(C4&gt;0,"Revisar entrega",SUMPRODUCT(J10:J107,--(F10:F107="F"))+SUMPRODUCT(K10:K107,--(G10:G107="F"))+SUMPRODUCT(L10:L107,--(H10:H107="F"))+SUMPRODUCT(M10:M107,--(I10:I107="F")))</x:f>
+        <x:f>IF(C4&gt;0,"Revisar entrega",SUMPRODUCT(J10:J111,--(F10:F111="F"))+SUMPRODUCT(K10:K111,--(G10:G111="F"))+SUMPRODUCT(L10:L111,--(H10:H111="F"))+SUMPRODUCT(M10:M111,--(I10:I111="F")))</x:f>
         <x:v>Revisar entrega</x:v>
       </x:c>
       <x:c r="J5" s="8" t="str">
@@ -6194,7 +6362,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q12" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 150 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 150 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -6402,7 +6570,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q16" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 570 × 99.55 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 570 × 99,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -6510,7 +6678,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q18" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 570 × 79.55 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 570 × 79,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -6718,7 +6886,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q22" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 640 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 640 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
@@ -6868,7 +7036,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q25" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 549.55 × 74.55 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 549,55 × 74,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
@@ -6922,7 +7090,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q26" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 583 × 74.55 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 583 × 74,55 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
@@ -7226,7 +7394,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q32" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 669.1 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 669,1 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
@@ -7528,7 +7696,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q38" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 370 × 99.1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 370 × 99,1 y cantear en el armado. Rebaje para la gola en el armado, cuando se defina el borde del granito; no lo hace el proveedor.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
@@ -7778,7 +7946,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q43" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 1274.1 × 96.1 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 1274,1 × 96,1 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
@@ -8292,7 +8460,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q53" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 569.1 × 59.1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 569,1 × 59,1 y cantear en el armado. P071: flexible 0,45 mm en los cuatro bordes. Confirmar cabida en canteadora; si la rechaza, cantear en taller con el descuento correspondiente.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
@@ -8806,7 +8974,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q63" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 684.1 × 59.1 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 684,1 × 59,1 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
@@ -8854,7 +9022,7 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q64" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 684.1 × 79.1 y cantear en el armado.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 684,1 × 79,1 y cantear en el armado.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
@@ -9423,22 +9591,22 @@
     </x:row>
     <x:row r="76" ht="58" customHeight="1">
       <x:c r="A76" s="8" t="str">
-        <x:v>Clóset C3-005</x:v>
+        <x:v>Clóset C3-025</x:v>
       </x:c>
       <x:c r="B76" s="10" t="str">
-        <x:v>Fondo RH15</x:v>
+        <x:v>Amarre posterior superior izquierdo</x:v>
       </x:c>
       <x:c r="C76" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D76" s="8" t="n">
-        <x:v>2250</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="E76" s="8" t="n">
-        <x:v>830</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F76" s="8" t="str">
-        <x:v>—</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="G76" s="8" t="str">
         <x:v>—</x:v>
@@ -9449,9 +9617,7 @@
       <x:c r="I76" s="8" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="J76" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="J76" s="11"/>
       <x:c r="K76" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -9461,19 +9627,20 @@
       <x:c r="M76" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N76" s="18" t="n">
+      <x:c r="N76" s="18" t="str">
         <x:f>IF(COUNT(J76:M76)&lt;4,"Por revisar",(IF(F76="R",J76*D76,0)+IF(G76="R",K76*D76,0)+IF(H76="R",L76*E76,0)+IF(I76="R",M76*E76,0))/1000)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O76" s="18" t="n">
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="O76" s="18" t="str">
         <x:f>IF(COUNT(J76:M76)&lt;4,"Por revisar",(IF(F76="F",J76*D76,0)+IF(G76="F",K76*D76,0)+IF(H76="F",L76*E76,0)+IF(I76="F",M76*E76,0))/1000)</x:f>
-        <x:v>0</x:v>
+        <x:v>Por revisar</x:v>
       </x:c>
       <x:c r="P76" s="8" t="str">
-        <x:v>SIN CANTO SOLICITADO</x:v>
+        <x:f>IF(COUNT(J76:M76)&lt;4,"POR REVISAR",IF(SUM(J76:M76)=0,"RECIBIDO CONFORME","CANTEAR A MANO"))</x:f>
+        <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q76" s="10" t="str">
-        <x:v>Sin canto</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
@@ -9746,22 +9913,22 @@
     </x:row>
     <x:row r="82" ht="58" customHeight="1">
       <x:c r="A82" s="8" t="str">
-        <x:v>Clóset C3-011</x:v>
+        <x:v>Clóset C3-026</x:v>
       </x:c>
       <x:c r="B82" s="10" t="str">
-        <x:v>Fondo RH15</x:v>
+        <x:v>Amarre posterior superior derecho</x:v>
       </x:c>
       <x:c r="C82" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D82" s="8" t="n">
-        <x:v>2250</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="E82" s="8" t="n">
-        <x:v>1075</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F82" s="8" t="str">
-        <x:v>—</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="G82" s="8" t="str">
         <x:v>—</x:v>
@@ -9772,9 +9939,7 @@
       <x:c r="I82" s="8" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="J82" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="J82" s="11"/>
       <x:c r="K82" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -9784,19 +9949,20 @@
       <x:c r="M82" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N82" s="18" t="n">
+      <x:c r="N82" s="18" t="str">
         <x:f>IF(COUNT(J82:M82)&lt;4,"Por revisar",(IF(F82="R",J82*D82,0)+IF(G82="R",K82*D82,0)+IF(H82="R",L82*E82,0)+IF(I82="R",M82*E82,0))/1000)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O82" s="18" t="n">
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="O82" s="18" t="str">
         <x:f>IF(COUNT(J82:M82)&lt;4,"Por revisar",(IF(F82="F",J82*D82,0)+IF(G82="F",K82*D82,0)+IF(H82="F",L82*E82,0)+IF(I82="F",M82*E82,0))/1000)</x:f>
-        <x:v>0</x:v>
+        <x:v>Por revisar</x:v>
       </x:c>
       <x:c r="P82" s="8" t="str">
-        <x:v>SIN CANTO SOLICITADO</x:v>
+        <x:f>IF(COUNT(J82:M82)&lt;4,"POR REVISAR",IF(SUM(J82:M82)=0,"RECIBIDO CONFORME","CANTEAR A MANO"))</x:f>
+        <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q82" s="10" t="str">
-        <x:v>Sin canto</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="58" customHeight="1">
@@ -10457,36 +10623,42 @@
     </x:row>
     <x:row r="96" ht="58" customHeight="1">
       <x:c r="A96" s="8" t="str">
-        <x:v>Baño B01</x:v>
+        <x:v>Clóset C3-027</x:v>
       </x:c>
       <x:c r="B96" s="10" t="str">
-        <x:v>Lateral</x:v>
+        <x:v>Montante posterior derecho</x:v>
       </x:c>
       <x:c r="C96" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D96" s="8" t="n">
-        <x:v>470</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="E96" s="8" t="n">
-        <x:v>450</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F96" s="8" t="str">
         <x:v>F</x:v>
       </x:c>
       <x:c r="G96" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="H96" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I96" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="J96" s="11"/>
-      <x:c r="K96" s="11"/>
-      <x:c r="L96" s="11"/>
-      <x:c r="M96" s="11"/>
+      <x:c r="K96" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L96" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M96" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="N96" s="18" t="str">
         <x:f>IF(COUNT(J96:M96)&lt;4,"Por revisar",(IF(F96="R",J96*D96,0)+IF(G96="R",K96*D96,0)+IF(H96="R",L96*E96,0)+IF(I96="R",M96*E96,0))/1000)</x:f>
         <x:v>Por revisar</x:v>
@@ -10500,41 +10672,47 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q96" s="10" t="str">
-        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="58" customHeight="1">
       <x:c r="A97" s="8" t="str">
-        <x:v>Baño B02</x:v>
+        <x:v>Clóset C3-028</x:v>
       </x:c>
       <x:c r="B97" s="10" t="str">
-        <x:v>Piso</x:v>
+        <x:v>Montante posterior izquierdo</x:v>
       </x:c>
       <x:c r="C97" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D97" s="8" t="n">
-        <x:v>490</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="E97" s="8" t="n">
-        <x:v>450</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F97" s="8" t="str">
         <x:v>F</x:v>
       </x:c>
       <x:c r="G97" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="H97" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I97" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="J97" s="11"/>
-      <x:c r="K97" s="11"/>
-      <x:c r="L97" s="11"/>
-      <x:c r="M97" s="11"/>
+      <x:c r="K97" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L97" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M97" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="N97" s="18" t="str">
         <x:f>IF(COUNT(J97:M97)&lt;4,"Por revisar",(IF(F97="R",J97*D97,0)+IF(G97="R",K97*D97,0)+IF(H97="R",L97*E97,0)+IF(I97="R",M97*E97,0))/1000)</x:f>
         <x:v>Por revisar</x:v>
@@ -10548,41 +10726,47 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q97" s="10" t="str">
-        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="58" customHeight="1">
       <x:c r="A98" s="8" t="str">
-        <x:v>Baño B03</x:v>
+        <x:v>Clóset C3-029</x:v>
       </x:c>
       <x:c r="B98" s="10" t="str">
-        <x:v>Entrepaño retranqueado con reserva de sifón</x:v>
+        <x:v>Amarre posterior inferior izquierdo</x:v>
       </x:c>
       <x:c r="C98" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D98" s="8" t="n">
-        <x:v>490</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="E98" s="8" t="n">
-        <x:v>405</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F98" s="8" t="str">
         <x:v>F</x:v>
       </x:c>
       <x:c r="G98" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="H98" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I98" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="J98" s="11"/>
-      <x:c r="K98" s="11"/>
-      <x:c r="L98" s="11"/>
-      <x:c r="M98" s="11"/>
+      <x:c r="K98" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M98" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="N98" s="18" t="str">
         <x:f>IF(COUNT(J98:M98)&lt;4,"Por revisar",(IF(F98="R",J98*D98,0)+IF(G98="R",K98*D98,0)+IF(H98="R",L98*E98,0)+IF(I98="R",M98*E98,0))/1000)</x:f>
         <x:v>Por revisar</x:v>
@@ -10596,41 +10780,47 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q98" s="10" t="str">
-        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="58" customHeight="1">
       <x:c r="A99" s="8" t="str">
-        <x:v>Baño B04</x:v>
+        <x:v>Clóset C3-030</x:v>
       </x:c>
       <x:c r="B99" s="10" t="str">
-        <x:v>Travesaño trasero superior lateral</x:v>
+        <x:v>Amarre posterior inferior derecho</x:v>
       </x:c>
       <x:c r="C99" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D99" s="8" t="n">
-        <x:v>195</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="E99" s="8" t="n">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F99" s="8" t="str">
         <x:v>F</x:v>
       </x:c>
       <x:c r="G99" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="H99" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I99" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="J99" s="11"/>
-      <x:c r="K99" s="11"/>
-      <x:c r="L99" s="11"/>
-      <x:c r="M99" s="11"/>
+      <x:c r="K99" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L99" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M99" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="N99" s="18" t="str">
         <x:f>IF(COUNT(J99:M99)&lt;4,"Por revisar",(IF(F99="R",J99*D99,0)+IF(G99="R",K99*D99,0)+IF(H99="R",L99*E99,0)+IF(I99="R",M99*E99,0))/1000)</x:f>
         <x:v>Por revisar</x:v>
@@ -10644,24 +10834,24 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q99" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="58" customHeight="1">
       <x:c r="A100" s="8" t="str">
-        <x:v>Baño B05</x:v>
+        <x:v>Baño B01</x:v>
       </x:c>
       <x:c r="B100" s="10" t="str">
-        <x:v>Travesaño trasero inferior</x:v>
+        <x:v>Lateral</x:v>
       </x:c>
       <x:c r="C100" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D100" s="8" t="n">
-        <x:v>490</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="E100" s="8" t="n">
-        <x:v>80</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="F100" s="8" t="str">
         <x:v>F</x:v>
@@ -10692,36 +10882,36 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q100" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="58" customHeight="1">
       <x:c r="A101" s="8" t="str">
-        <x:v>Baño B06</x:v>
+        <x:v>Baño B02</x:v>
       </x:c>
       <x:c r="B101" s="10" t="str">
-        <x:v>Panel común para dos puertas: corte diagonal en armado</x:v>
+        <x:v>Piso</x:v>
       </x:c>
       <x:c r="C101" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D101" s="8" t="n">
-        <x:v>299</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E101" s="8" t="n">
-        <x:v>517</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="F101" s="8" t="str">
-        <x:v>R</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="G101" s="8" t="str">
-        <x:v>R</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="H101" s="8" t="str">
-        <x:v>R</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="I101" s="8" t="str">
-        <x:v>R</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="J101" s="11"/>
       <x:c r="K101" s="11"/>
@@ -10740,24 +10930,24 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q101" s="10" t="str">
-        <x:v>Normal · Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</x:v>
+        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="58" customHeight="1">
       <x:c r="A102" s="8" t="str">
-        <x:v>Baño S01</x:v>
+        <x:v>Baño B03</x:v>
       </x:c>
       <x:c r="B102" s="10" t="str">
-        <x:v>Lateral gabinete superior</x:v>
+        <x:v>Entrepaño retranqueado con reserva de sifón</x:v>
       </x:c>
       <x:c r="C102" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D102" s="8" t="n">
-        <x:v>500</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E102" s="8" t="n">
-        <x:v>105</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F102" s="8" t="str">
         <x:v>F</x:v>
@@ -10788,24 +10978,24 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q102" s="10" t="str">
-        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Nicho libre de 150 mm bajo granito. Recorte trasero ilustrativo 100 × 270 mm, centrado; no mecanizar sin sifón real. Retranqueo frontal de 30 mm para agarre. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="58" customHeight="1">
       <x:c r="A103" s="8" t="str">
-        <x:v>Baño S02</x:v>
+        <x:v>Baño B04</x:v>
       </x:c>
       <x:c r="B103" s="10" t="str">
-        <x:v>Piso y techo gabinete superior</x:v>
+        <x:v>Travesaño trasero superior lateral</x:v>
       </x:c>
       <x:c r="C103" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D103" s="8" t="n">
-        <x:v>420</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E103" s="8" t="n">
-        <x:v>105</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F103" s="8" t="str">
         <x:v>F</x:v>
@@ -10836,24 +11026,24 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q103" s="10" t="str">
-        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 194.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. De canto, interrumpido en el centro para tuberías; no es un colgador certificado. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="58" customHeight="1">
       <x:c r="A104" s="8" t="str">
-        <x:v>Baño S03</x:v>
+        <x:v>Baño B05</x:v>
       </x:c>
       <x:c r="B104" s="10" t="str">
-        <x:v>División vertical</x:v>
+        <x:v>Travesaño trasero inferior</x:v>
       </x:c>
       <x:c r="C104" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D104" s="8" t="n">
-        <x:v>470</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E104" s="8" t="n">
-        <x:v>105</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F104" s="8" t="str">
         <x:v>F</x:v>
@@ -10884,36 +11074,36 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q104" s="10" t="str">
-        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Pequeña · Si no la cantean: cortar a 489.1 × 79.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Define rigidez posterior; anclajes y uniones por dimensionar. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="58" customHeight="1">
       <x:c r="A105" s="8" t="str">
-        <x:v>Baño S04</x:v>
+        <x:v>Baño B06</x:v>
       </x:c>
       <x:c r="B105" s="10" t="str">
-        <x:v>Entrepaño interior izquierdo</x:v>
+        <x:v>Panel común para dos puertas: corte diagonal en armado</x:v>
       </x:c>
       <x:c r="C105" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D105" s="8" t="n">
-        <x:v>290</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E105" s="8" t="n">
-        <x:v>100</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F105" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>R</x:v>
       </x:c>
       <x:c r="G105" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>R</x:v>
       </x:c>
       <x:c r="H105" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>R</x:v>
       </x:c>
       <x:c r="I105" s="8" t="str">
-        <x:v>F</x:v>
+        <x:v>R</x:v>
       </x:c>
       <x:c r="J105" s="11"/>
       <x:c r="K105" s="11"/>
@@ -10932,24 +11122,24 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q105" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Normal · Una sola pieza rectangular terminada 517 × 299 mm (veta vertical). Pedirla entera, con canto 2 mm en el perímetro; NO dividir en tienda. En el armado, corte central a 75° de la horizontal (provisional entre 70 y 80°) con el disco Diablo de 1,5 mm (corte de 0,059") y canto flexible 0,45 mm en los dos bordes nuevos. Holgura entre puertas tras cantear ≈0,6 mm: probablemente insuficiente (ver Pendientes). La medida de lista es del panel común, no de cada tapa.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="58" customHeight="1">
       <x:c r="A106" s="8" t="str">
-        <x:v>Baño S05</x:v>
+        <x:v>Baño S01</x:v>
       </x:c>
       <x:c r="B106" s="10" t="str">
-        <x:v>Entrepaño columna abierta derecha</x:v>
+        <x:v>Lateral gabinete superior</x:v>
       </x:c>
       <x:c r="C106" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D106" s="8" t="n">
-        <x:v>115</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E106" s="8" t="n">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F106" s="8" t="str">
         <x:v>F</x:v>
@@ -10980,24 +11170,24 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q106" s="10" t="str">
-        <x:v>Pequeña · Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Fondo total 130 mm con panel 6 mm, holgura frontal 1 mm, tapa RH15 y espejo 3 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="58" customHeight="1">
       <x:c r="A107" s="8" t="str">
-        <x:v>Baño S06</x:v>
+        <x:v>Baño S02</x:v>
       </x:c>
       <x:c r="B107" s="10" t="str">
-        <x:v>Tapa RH15 portadora del espejo</x:v>
+        <x:v>Piso y techo gabinete superior</x:v>
       </x:c>
       <x:c r="C107" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D107" s="8" t="n">
-        <x:v>500</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E107" s="8" t="n">
-        <x:v>320</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F107" s="8" t="str">
         <x:v>F</x:v>
@@ -11028,6 +11218,198 @@
         <x:v>POR REVISAR</x:v>
       </x:c>
       <x:c r="Q107" s="10" t="str">
+        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="58" customHeight="1">
+      <x:c r="A108" s="8" t="str">
+        <x:v>Baño S03</x:v>
+      </x:c>
+      <x:c r="B108" s="10" t="str">
+        <x:v>División vertical</x:v>
+      </x:c>
+      <x:c r="C108" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D108" s="8" t="n">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="E108" s="8" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F108" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G108" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H108" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I108" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J108" s="11"/>
+      <x:c r="K108" s="11"/>
+      <x:c r="L108" s="11"/>
+      <x:c r="M108" s="11"/>
+      <x:c r="N108" s="18" t="str">
+        <x:f>IF(COUNT(J108:M108)&lt;4,"Por revisar",(IF(F108="R",J108*D108,0)+IF(G108="R",K108*D108,0)+IF(H108="R",L108*E108,0)+IF(I108="R",M108*E108,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="O108" s="18" t="str">
+        <x:f>IF(COUNT(J108:M108)&lt;4,"Por revisar",(IF(F108="F",J108*D108,0)+IF(G108="F",K108*D108,0)+IF(H108="F",L108*E108,0)+IF(I108="F",M108*E108,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="P108" s="8" t="str">
+        <x:f>IF(COUNT(J108:M108)&lt;4,"POR REVISAR",IF(SUM(J108:M108)=0,"RECIBIDO CONFORME","CANTEAR A MANO"))</x:f>
+        <x:v>POR REVISAR</x:v>
+      </x:c>
+      <x:c r="Q108" s="10" t="str">
+        <x:v>Normal · Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Interior cerrado 290 mm; columna derecha abierta 115 mm. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="58" customHeight="1">
+      <x:c r="A109" s="8" t="str">
+        <x:v>Baño S04</x:v>
+      </x:c>
+      <x:c r="B109" s="10" t="str">
+        <x:v>Entrepaño interior izquierdo</x:v>
+      </x:c>
+      <x:c r="C109" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D109" s="8" t="n">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="E109" s="8" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F109" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G109" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H109" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I109" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J109" s="11"/>
+      <x:c r="K109" s="11"/>
+      <x:c r="L109" s="11"/>
+      <x:c r="M109" s="11"/>
+      <x:c r="N109" s="18" t="str">
+        <x:f>IF(COUNT(J109:M109)&lt;4,"Por revisar",(IF(F109="R",J109*D109,0)+IF(G109="R",K109*D109,0)+IF(H109="R",L109*E109,0)+IF(I109="R",M109*E109,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="O109" s="18" t="str">
+        <x:f>IF(COUNT(J109:M109)&lt;4,"Por revisar",(IF(F109="F",J109*D109,0)+IF(G109="F",K109*D109,0)+IF(H109="F",L109*E109,0)+IF(I109="F",M109*E109,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="P109" s="8" t="str">
+        <x:f>IF(COUNT(J109:M109)&lt;4,"POR REVISAR",IF(SUM(J109:M109)=0,"RECIBIDO CONFORME","CANTEAR A MANO"))</x:f>
+        <x:v>POR REVISAR</x:v>
+      </x:c>
+      <x:c r="Q109" s="10" t="str">
+        <x:v>Pequeña · Si no la cantean: cortar a 289.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Dos entrepaños fijos como la referencia. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="58" customHeight="1">
+      <x:c r="A110" s="8" t="str">
+        <x:v>Baño S05</x:v>
+      </x:c>
+      <x:c r="B110" s="10" t="str">
+        <x:v>Entrepaño columna abierta derecha</x:v>
+      </x:c>
+      <x:c r="C110" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D110" s="8" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E110" s="8" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F110" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G110" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H110" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I110" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J110" s="11"/>
+      <x:c r="K110" s="11"/>
+      <x:c r="L110" s="11"/>
+      <x:c r="M110" s="11"/>
+      <x:c r="N110" s="18" t="str">
+        <x:f>IF(COUNT(J110:M110)&lt;4,"Por revisar",(IF(F110="R",J110*D110,0)+IF(G110="R",K110*D110,0)+IF(H110="R",L110*E110,0)+IF(I110="R",M110*E110,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="O110" s="18" t="str">
+        <x:f>IF(COUNT(J110:M110)&lt;4,"Por revisar",(IF(F110="F",J110*D110,0)+IF(G110="F",K110*D110,0)+IF(H110="F",L110*E110,0)+IF(I110="F",M110*E110,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="P110" s="8" t="str">
+        <x:f>IF(COUNT(J110:M110)&lt;4,"POR REVISAR",IF(SUM(J110:M110)=0,"RECIBIDO CONFORME","CANTEAR A MANO"))</x:f>
+        <x:v>POR REVISAR</x:v>
+      </x:c>
+      <x:c r="Q110" s="10" t="str">
+        <x:v>Pequeña · Si no la cantean: cortar a 114.1 × 99.1 y cantear en taller. Zona húmeda: proteger todos los bordes y sellar perforaciones; dimensiones terminadas. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="58" customHeight="1">
+      <x:c r="A111" s="8" t="str">
+        <x:v>Baño S06</x:v>
+      </x:c>
+      <x:c r="B111" s="10" t="str">
+        <x:v>Tapa RH15 portadora del espejo</x:v>
+      </x:c>
+      <x:c r="C111" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D111" s="8" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E111" s="8" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="F111" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H111" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I111" s="8" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J111" s="11"/>
+      <x:c r="K111" s="11"/>
+      <x:c r="L111" s="11"/>
+      <x:c r="M111" s="11"/>
+      <x:c r="N111" s="18" t="str">
+        <x:f>IF(COUNT(J111:M111)&lt;4,"Por revisar",(IF(F111="R",J111*D111,0)+IF(G111="R",K111*D111,0)+IF(H111="R",L111*E111,0)+IF(I111="R",M111*E111,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="O111" s="18" t="str">
+        <x:f>IF(COUNT(J111:M111)&lt;4,"Por revisar",(IF(F111="F",J111*D111,0)+IF(G111="F",K111*D111,0)+IF(H111="F",L111*E111,0)+IF(I111="F",M111*E111,0))/1000)</x:f>
+        <x:v>Por revisar</x:v>
+      </x:c>
+      <x:c r="P111" s="8" t="str">
+        <x:f>IF(COUNT(J111:M111)&lt;4,"POR REVISAR",IF(SUM(J111:M111)=0,"RECIBIDO CONFORME","CANTEAR A MANO"))</x:f>
+        <x:v>POR REVISAR</x:v>
+      </x:c>
+      <x:c r="Q111" s="10" t="str">
         <x:v>Normal · Medida exterior de referencia 320 × 500; espejo pegado en cara exterior. Dos bisagras candidatas, peso conjunto aproximado 2,8 kg sin herrajes. Validar holguras, cazoletas y adhesivo compatible con espejo. Canto flexible 0,45 mm en todo el perímetro; mantener sellados recortes y perforaciones.</x:v>
       </x:c>
     </x:row>
@@ -11035,7 +11417,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A3:Q3"/>
   </x:mergeCells>
-  <x:dataValidations count="392">
+  <x:dataValidations count="408">
     <x:dataValidation type="whole" operator="between" sqref="J10">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
@@ -12414,193 +12796,257 @@
     </x:dataValidation>
     <x:dataValidation type="whole" operator="between" sqref="J96">
       <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K96">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L96">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M96">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J97">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K97">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L97">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M97">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J98">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K98">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L98">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M98">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J99">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K99">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L99">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M99">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J100">
+      <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K96">
+    <x:dataValidation type="whole" operator="between" sqref="K100">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L96">
+    <x:dataValidation type="whole" operator="between" sqref="L100">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M96">
+    <x:dataValidation type="whole" operator="between" sqref="M100">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J97">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K97">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L97">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M97">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J98">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K98">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L98">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M98">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J99">
+    <x:dataValidation type="whole" operator="between" sqref="J101">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K101">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L101">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M101">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J102">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K102">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L102">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M102">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J103">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K99">
+    <x:dataValidation type="whole" operator="between" sqref="K103">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L99">
+    <x:dataValidation type="whole" operator="between" sqref="L103">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M99">
+    <x:dataValidation type="whole" operator="between" sqref="M103">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J100">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K100">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L100">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M100">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J101">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K101">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L101">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M101">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J102">
+    <x:dataValidation type="whole" operator="between" sqref="J104">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K104">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L104">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M104">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J105">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K105">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L105">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M105">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J106">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K102">
+    <x:dataValidation type="whole" operator="between" sqref="K106">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L102">
+    <x:dataValidation type="whole" operator="between" sqref="L106">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M102">
+    <x:dataValidation type="whole" operator="between" sqref="M106">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J103">
+    <x:dataValidation type="whole" operator="between" sqref="J107">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K103">
+    <x:dataValidation type="whole" operator="between" sqref="K107">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L103">
+    <x:dataValidation type="whole" operator="between" sqref="L107">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M103">
+    <x:dataValidation type="whole" operator="between" sqref="M107">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J104">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K104">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L104">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M104">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J105">
+    <x:dataValidation type="whole" operator="between" sqref="J108">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K108">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L108">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M108">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J109">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K105">
+    <x:dataValidation type="whole" operator="between" sqref="K109">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L105">
+    <x:dataValidation type="whole" operator="between" sqref="L109">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M105">
+    <x:dataValidation type="whole" operator="between" sqref="M109">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J106">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K106">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L106">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M106">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J107">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K107">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L107">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M107">
+    <x:dataValidation type="whole" operator="between" sqref="J110">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K110">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L110">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M110">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="J111">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K111">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L111">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="M111">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
     </x:dataValidation>
